--- a/database/excels/myprofile/base-seeder.xlsx
+++ b/database/excels/myprofile/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myprofile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C99DC8-2620-AD4F-A9F8-FBAD162FFCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECA620D-CFC8-D54E-BD0C-C1037C8083C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>myprofile-family</t>
   </si>
   <si>
-    <t>assignment_ind</t>
-  </si>
-  <si>
     <t>indigo</t>
   </si>
   <si>
@@ -231,6 +228,9 @@
   </si>
   <si>
     <t>Dokumen</t>
+  </si>
+  <si>
+    <t>badge</t>
   </si>
 </sst>
 </file>
@@ -647,16 +647,16 @@
         <v>25</v>
       </c>
       <c r="D2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -738,19 +738,19 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" t="s">
         <v>62</v>
-      </c>
-      <c r="D3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" t="s">
-        <v>63</v>
       </c>
       <c r="G3" s="4" t="b">
         <v>1</v>
@@ -764,10 +764,10 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>23</v>
@@ -776,7 +776,7 @@
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G4" s="4" t="b">
         <v>1</v>
@@ -790,19 +790,19 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="b">
         <v>1</v>
@@ -822,13 +822,13 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G6" s="4" t="b">
         <v>0</v>
@@ -848,13 +848,13 @@
         <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G7" s="4" t="b">
         <v>0</v>
@@ -874,13 +874,13 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G8" s="4" t="b">
         <v>0</v>
@@ -900,13 +900,13 @@
         <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G9" s="4" t="b">
         <v>0</v>
@@ -932,7 +932,7 @@
         <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10" s="4" t="b">
         <v>0</v>
@@ -952,13 +952,13 @@
         <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11" s="4" t="b">
         <v>0</v>
@@ -1008,10 +1008,10 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1019,10 +1019,10 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1030,10 +1030,10 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1044,7 +1044,7 @@
         <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
@@ -1055,7 +1055,7 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
@@ -1066,7 +1066,7 @@
         <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
@@ -1077,7 +1077,7 @@
         <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
@@ -1088,7 +1088,7 @@
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
@@ -1099,7 +1099,7 @@
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1137,7 +1137,7 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1170,7 +1170,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -1181,10 +1181,10 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
         <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -1192,10 +1192,10 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -1203,10 +1203,10 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -1214,7 +1214,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -1225,7 +1225,7 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -1236,7 +1236,7 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -1247,7 +1247,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -1258,7 +1258,7 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -1269,7 +1269,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>
@@ -1308,7 +1308,7 @@
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -1322,10 +1322,10 @@
         <v>25</v>
       </c>
       <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
         <v>61</v>
-      </c>
-      <c r="C3" t="s">
-        <v>62</v>
       </c>
       <c r="D3" t="s">
         <v>17</v>
@@ -1336,10 +1336,10 @@
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
         <v>17</v>
@@ -1350,10 +1350,10 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
         <v>17</v>
@@ -1364,7 +1364,7 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -1378,7 +1378,7 @@
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -1392,7 +1392,7 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
         <v>34</v>
@@ -1406,7 +1406,7 @@
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
         <v>35</v>
@@ -1420,7 +1420,7 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
         <v>36</v>
@@ -1434,7 +1434,7 @@
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>37</v>

--- a/database/excels/myprofile/base-seeder.xlsx
+++ b/database/excels/myprofile/base-seeder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/monoland/Platform/monoland/database/excels/myprofile/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECA620D-CFC8-D54E-BD0C-C1037C8083C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2EF3D9-C253-AF4C-8700-F667BC7C29D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{94E1010F-4E68-D749-BBCF-3803F804C4FE}"/>
   </bookViews>
   <sheets>
     <sheet name="module" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="68">
   <si>
     <t>name</t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>badge</t>
+  </si>
+  <si>
+    <t>title</t>
   </si>
 </sst>
 </file>
@@ -666,19 +669,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF7F25A-0145-E049-BABB-6C723A859E1D}">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="51.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.83203125" style="4"/>
-    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="51.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.83203125" style="4"/>
+    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
@@ -686,54 +690,57 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>25</v>
-      </c>
       <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="4" t="b">
+      <c r="H2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="b">
+      <c r="I2" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -741,25 +748,28 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" t="s">
-        <v>25</v>
-      </c>
       <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
         <v>62</v>
       </c>
-      <c r="G3" s="4" t="b">
+      <c r="H3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="4" t="b">
+      <c r="I3" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>25</v>
       </c>
@@ -767,25 +777,28 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>23</v>
       </c>
-      <c r="E4" t="s">
-        <v>25</v>
-      </c>
       <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
         <v>51</v>
       </c>
-      <c r="G4" s="4" t="b">
+      <c r="H4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="b">
+      <c r="I4" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -793,25 +806,28 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
         <v>43</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
       <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="4" t="b">
+      <c r="H5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="b">
+      <c r="I5" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -819,25 +835,28 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>44</v>
       </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
       <c r="F6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" t="s">
         <v>50</v>
       </c>
-      <c r="G6" s="4" t="b">
+      <c r="H6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H6" s="4" t="b">
+      <c r="I6" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -845,25 +864,28 @@
         <v>21</v>
       </c>
       <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>33</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
-        <v>25</v>
-      </c>
       <c r="F7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="4" t="b">
+      <c r="H7" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="b">
+      <c r="I7" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -871,25 +893,28 @@
         <v>22</v>
       </c>
       <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>47</v>
       </c>
-      <c r="E8" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" t="s">
         <v>54</v>
       </c>
-      <c r="G8" s="4" t="b">
+      <c r="H8" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="4" t="b">
+      <c r="I8" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>25</v>
       </c>
@@ -897,25 +922,28 @@
         <v>28</v>
       </c>
       <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
-        <v>25</v>
-      </c>
       <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="4" t="b">
+      <c r="H9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="b">
+      <c r="I9" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>25</v>
       </c>
@@ -923,25 +951,28 @@
         <v>29</v>
       </c>
       <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>24</v>
       </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
       <c r="F10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" t="s">
         <v>56</v>
       </c>
-      <c r="G10" s="4" t="b">
+      <c r="H10" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="b">
+      <c r="I10" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -949,21 +980,24 @@
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
       <c r="F11" t="s">
+        <v>25</v>
+      </c>
+      <c r="G11" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="4" t="b">
+      <c r="H11" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="b">
+      <c r="I11" s="4" t="b">
         <v>1</v>
       </c>
     </row>
